--- a/dati/CONSEGNE/CONSEGNE_20-04-2026/punti_consegna.xlsx
+++ b/dati/CONSEGNE/CONSEGNE_20-04-2026/punti_consegna.xlsx
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>45.46527050981497</v>
+        <v>45.39191463806938</v>
       </c>
       <c r="J22" t="n">
-        <v>12.11488789812301</v>
+        <v>12.02258055857691</v>
       </c>
     </row>
     <row r="23">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>45.46527050981497</v>
+        <v>45.39191463806938</v>
       </c>
       <c r="J118" t="n">
-        <v>12.11488789812301</v>
+        <v>12.02258055857691</v>
       </c>
     </row>
     <row r="119">
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>45.4266008</v>
+        <v>45.42661711426619</v>
       </c>
       <c r="J120" t="n">
-        <v>12.0702557</v>
+        <v>12.07021814907378</v>
       </c>
     </row>
     <row r="121">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>45.46527050981497</v>
+        <v>45.39191463806938</v>
       </c>
       <c r="J127" t="n">
-        <v>12.11488789812301</v>
+        <v>12.02258055857691</v>
       </c>
     </row>
     <row r="128">

--- a/dati/CONSEGNE/CONSEGNE_20-04-2026/punti_consegna.xlsx
+++ b/dati/CONSEGNE/CONSEGNE_20-04-2026/punti_consegna.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="27100" yWindow="690" windowWidth="18990" windowHeight="12750" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$162</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +51,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,7 +415,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="11.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.90625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.81640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="4.90625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="52.90625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="63.81640625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="9.81640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10.1796875" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="11.81640625" bestFit="1" customWidth="1" min="9" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1428,10 +1440,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>45.39191463806938</v>
+        <v>45.46527050981497</v>
       </c>
       <c r="J22" t="n">
-        <v>12.02258055857691</v>
+        <v>12.11488789812301</v>
       </c>
     </row>
     <row r="23">
@@ -2762,10 +2774,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>45.19902387104506</v>
+        <v>45.50311539552625</v>
       </c>
       <c r="J51" t="n">
-        <v>12.28924665740635</v>
+        <v>11.42255497443841</v>
       </c>
     </row>
     <row r="52">
@@ -3728,10 +3740,10 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>45.3880594</v>
+        <v>45.49352284190952</v>
       </c>
       <c r="J72" t="n">
-        <v>12.0101781</v>
+        <v>12.25899592537706</v>
       </c>
     </row>
     <row r="73">
@@ -5844,10 +5856,10 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>45.39191463806938</v>
+        <v>45.42695237766134</v>
       </c>
       <c r="J118" t="n">
-        <v>12.02258055857691</v>
+        <v>12.07789843304362</v>
       </c>
     </row>
     <row r="119">
@@ -7875,6 +7887,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>